--- a/tablero/uploads/Vector Ajuste Data Histórica.xlsx
+++ b/tablero/uploads/Vector Ajuste Data Histórica.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aminerals-my.sharepoint.com/personal/mmadrida_pelambres_cl1/Documents/Documentos/Control Gestión 2026/Presupuesto Corporativo/Vector Ajuste/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amsmmadrida\Repositorios Personales Control Gestion\amsa-budget-corporativo\tablero\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="234" documentId="11_AD4D2F04E46CFB4ACB3E20581593C05A683EDF21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B02098D0-971A-4AB6-BAE9-644764F44D58}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F4F115-737C-4899-8810-4439B7D344FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,9 @@
   </sheets>
   <definedNames>
     <definedName name="DOLAR_OBS_ADO" localSheetId="0">Hoja1!$A$4:$AM$6</definedName>
+    <definedName name="DOLAR_OBS_ADO_1" localSheetId="0">Hoja1!$A$12:$AM$14</definedName>
+    <definedName name="DOLAR_OBS_ADO_2" localSheetId="0">Hoja1!$A$20:$AM$22</definedName>
+    <definedName name="DOLAR_OBS_ADO_3" localSheetId="0">Hoja1!$A$28:$AM$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,6 +47,12 @@
     <author>tc={E388792B-3538-475A-A757-4280E8F8BA23}</author>
     <author>tc={EEC41950-6022-427A-B5EF-C10980E7C5E0}</author>
     <author>Michelle Madrid Araya</author>
+    <author>tc={9F2CFE62-0FBF-427C-A3D7-CE6A2626B092}</author>
+    <author>tc={393151C9-8594-4A72-A728-6E5BB649AF4D}</author>
+    <author>tc={7D5D9D06-3A77-4519-9FE9-7C2A54490A0A}</author>
+    <author>tc={0A050290-AA01-430C-ADCE-D319815F4916}</author>
+    <author>tc={88033D7C-3197-4733-8F1C-B124922716CB}</author>
+    <author>tc={A0044274-CA02-4FE0-8A5C-DF1392887D40}</author>
   </authors>
   <commentList>
     <comment ref="C4" authorId="0" shapeId="0" xr:uid="{E388792B-3538-475A-A757-4280E8F8BA23}">
@@ -87,6 +96,129 @@
         </r>
       </text>
     </comment>
+    <comment ref="C12" authorId="3" shapeId="0" xr:uid="{9F2CFE62-0FBF-427C-A3D7-CE6A2626B092}">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Fuente: INE Chile, Serie histórica empalmada IPC base 2023=100 (archivo: serie-histórica-empalmada-ipc-diciembre-2009-a-la-fecha-xls.xlsx)</t>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="4" shapeId="0" xr:uid="{393151C9-8594-4A72-A728-6E5BB649AF4D}">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Fuente: UF_IVP_UTM_F.xlsx, hoja Cuadro (UF fin de mes)</t>
+      </text>
+    </comment>
+    <comment ref="BD15" authorId="2" shapeId="0" xr:uid="{E978CB9E-565D-49EC-9975-00B351CE88CB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Michelle Madrid Araya:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Real
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="5" shapeId="0" xr:uid="{7D5D9D06-3A77-4519-9FE9-7C2A54490A0A}">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Fuente: INE Chile, Serie histórica empalmada IPC base 2023=100 (archivo: serie-histórica-empalmada-ipc-diciembre-2009-a-la-fecha-xls.xlsx)</t>
+      </text>
+    </comment>
+    <comment ref="C23" authorId="6" shapeId="0" xr:uid="{0A050290-AA01-430C-ADCE-D319815F4916}">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Fuente: UF_IVP_UTM_F.xlsx, hoja Cuadro (UF fin de mes)</t>
+      </text>
+    </comment>
+    <comment ref="BD23" authorId="2" shapeId="0" xr:uid="{E0A222B7-95F5-479C-AF59-B72FE2256434}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Michelle Madrid Araya:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Real
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C28" authorId="7" shapeId="0" xr:uid="{88033D7C-3197-4733-8F1C-B124922716CB}">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Fuente: INE Chile, Serie histórica empalmada IPC base 2023=100 (archivo: serie-histórica-empalmada-ipc-diciembre-2009-a-la-fecha-xls.xlsx)</t>
+      </text>
+    </comment>
+    <comment ref="C31" authorId="8" shapeId="0" xr:uid="{A0044274-CA02-4FE0-8A5C-DF1392887D40}">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Fuente: UF_IVP_UTM_F.xlsx, hoja Cuadro (UF fin de mes)</t>
+      </text>
+    </comment>
+    <comment ref="BD31" authorId="2" shapeId="0" xr:uid="{C4876CDF-1C8D-4B31-99CE-FAC6F97F9E8B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Michelle Madrid Araya:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Real
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -100,11 +232,32 @@
       <parameter name="añoFinal" prompt="Año final"/>
     </parameters>
   </connection>
+  <connection id="2" xr16:uid="{87FA9FD6-E93E-441F-BD07-442A6AEC90B7}" odcFile="Z:\01 Control de Gestión\02 Control de Gestion\2016\2016-03\Flash Report\Anexos\DOLAR_OBS_ADO.iqy" name="DOLAR_OBS_ADO1" type="4" refreshedVersion="4" background="1" saveData="1">
+    <webPr consecutive="1" xl2000="1" url="http://si3.bcentral.cl/SieteIQY/secure/carga_series_excel.aspx" post="fechaInicio=[&quot;añoInicial&quot;,&quot;Año inicial&quot;]&amp;fechaFin=[&quot;añoFinal&quot;,&quot;Año final&quot;]&amp;param=Wkw0YXVsWGl5eGRyblFhNTczJmFoczhpaDF2Li1DXyZkUmJHekUzJnMyQWtkLjVfTEZqdS1BMS1ELkt4Jm9lMTFRYTd0RHNGJCBhaiBTYTVyJFUgKC45ZzhBIDdiZiA5w7M4MFIpJmJIMDB3TkJFM0R3RzV2JHAkOE9pWCNheV9DVGp6RSQ2U1VUX24wVUZxw7M0TyQgVXlrMHN6alJuOzJ1Nm5ZLmpWN29GRHZBTUxIMFE4RWUyb1VOVjgwQzRWdE/Ds3JEbyB1X0Q0SyRG" htmlTables="1" htmlFormat="all"/>
+    <parameters count="2">
+      <parameter name="añoInicial" prompt="Año inicial"/>
+      <parameter name="añoFinal" prompt="Año final"/>
+    </parameters>
+  </connection>
+  <connection id="3" xr16:uid="{138FA4FE-4D7F-415A-B766-631ECECE2B8F}" odcFile="Z:\01 Control de Gestión\02 Control de Gestion\2016\2016-03\Flash Report\Anexos\DOLAR_OBS_ADO.iqy" name="DOLAR_OBS_ADO2" type="4" refreshedVersion="4" background="1" saveData="1">
+    <webPr consecutive="1" xl2000="1" url="http://si3.bcentral.cl/SieteIQY/secure/carga_series_excel.aspx" post="fechaInicio=[&quot;añoInicial&quot;,&quot;Año inicial&quot;]&amp;fechaFin=[&quot;añoFinal&quot;,&quot;Año final&quot;]&amp;param=Wkw0YXVsWGl5eGRyblFhNTczJmFoczhpaDF2Li1DXyZkUmJHekUzJnMyQWtkLjVfTEZqdS1BMS1ELkt4Jm9lMTFRYTd0RHNGJCBhaiBTYTVyJFUgKC45ZzhBIDdiZiA5w7M4MFIpJmJIMDB3TkJFM0R3RzV2JHAkOE9pWCNheV9DVGp6RSQ2U1VUX24wVUZxw7M0TyQgVXlrMHN6alJuOzJ1Nm5ZLmpWN29GRHZBTUxIMFE4RWUyb1VOVjgwQzRWdE/Ds3JEbyB1X0Q0SyRG" htmlTables="1" htmlFormat="all"/>
+    <parameters count="2">
+      <parameter name="añoInicial" prompt="Año inicial"/>
+      <parameter name="añoFinal" prompt="Año final"/>
+    </parameters>
+  </connection>
+  <connection id="4" xr16:uid="{2CB6BA14-D2B2-4AB2-9427-28F33EE58F5C}" odcFile="Z:\01 Control de Gestión\02 Control de Gestion\2016\2016-03\Flash Report\Anexos\DOLAR_OBS_ADO.iqy" name="DOLAR_OBS_ADO3" type="4" refreshedVersion="4" background="1" saveData="1">
+    <webPr consecutive="1" xl2000="1" url="http://si3.bcentral.cl/SieteIQY/secure/carga_series_excel.aspx" post="fechaInicio=[&quot;añoInicial&quot;,&quot;Año inicial&quot;]&amp;fechaFin=[&quot;añoFinal&quot;,&quot;Año final&quot;]&amp;param=Wkw0YXVsWGl5eGRyblFhNTczJmFoczhpaDF2Li1DXyZkUmJHekUzJnMyQWtkLjVfTEZqdS1BMS1ELkt4Jm9lMTFRYTd0RHNGJCBhaiBTYTVyJFUgKC45ZzhBIDdiZiA5w7M4MFIpJmJIMDB3TkJFM0R3RzV2JHAkOE9pWCNheV9DVGp6RSQ2U1VUX24wVUZxw7M0TyQgVXlrMHN6alJuOzJ1Nm5ZLmpWN29GRHZBTUxIMFE4RWUyb1VOVjgwQzRWdE/Ds3JEbyB1X0Q0SyRG" htmlTables="1" htmlFormat="all"/>
+    <parameters count="2">
+      <parameter name="añoInicial" prompt="Año inicial"/>
+      <parameter name="añoFinal" prompt="Año final"/>
+    </parameters>
+  </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="83">
   <si>
     <t>Real</t>
   </si>
@@ -338,6 +491,21 @@
   </si>
   <si>
     <t>CLP/UF</t>
+  </si>
+  <si>
+    <t>Presupuesto</t>
+  </si>
+  <si>
+    <t>Forecast 5+6 2026</t>
+  </si>
+  <si>
+    <t>Forecast 5+6</t>
+  </si>
+  <si>
+    <t>Outlook 6+6 2026</t>
+  </si>
+  <si>
+    <t>Outlook 6+6</t>
   </si>
 </sst>
 </file>
@@ -404,7 +572,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -429,6 +597,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -443,7 +617,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -468,6 +642,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -495,6 +672,18 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="DOLAR_OBS_ADO_3" preserveFormatting="0" connectionId="4" xr16:uid="{1A81FDA6-2994-406F-B8D5-2504C4CC48A6}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="DOLAR_OBS_ADO_2" preserveFormatting="0" connectionId="3" xr16:uid="{F3F2CB51-1BDC-4F2C-8F28-69AF521ABD79}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="DOLAR_OBS_ADO_1" preserveFormatting="0" connectionId="2" xr16:uid="{3BAE89B8-646B-466C-946C-2E20CADB0863}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="DOLAR_OBS_ADO" preserveFormatting="0" connectionId="1" xr16:uid="{19AE37AA-B59B-48F4-B557-DF0F7B3A9E3E}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
@@ -767,6 +956,24 @@
   <threadedComment ref="C7" dT="2026-07-02T15:34:13.48" personId="{50860DAD-A217-40AC-975A-03A6080E2F06}" id="{EEC41950-6022-427A-B5EF-C10980E7C5E0}">
     <text>Fuente: UF_IVP_UTM_F.xlsx, hoja Cuadro (UF fin de mes)</text>
   </threadedComment>
+  <threadedComment ref="C12" dT="2026-07-02T15:42:20.92" personId="{50860DAD-A217-40AC-975A-03A6080E2F06}" id="{9F2CFE62-0FBF-427C-A3D7-CE6A2626B092}">
+    <text>Fuente: INE Chile, Serie histórica empalmada IPC base 2023=100 (archivo: serie-histórica-empalmada-ipc-diciembre-2009-a-la-fecha-xls.xlsx)</text>
+  </threadedComment>
+  <threadedComment ref="C15" dT="2026-07-02T15:34:13.48" personId="{50860DAD-A217-40AC-975A-03A6080E2F06}" id="{393151C9-8594-4A72-A728-6E5BB649AF4D}">
+    <text>Fuente: UF_IVP_UTM_F.xlsx, hoja Cuadro (UF fin de mes)</text>
+  </threadedComment>
+  <threadedComment ref="C20" dT="2026-07-02T15:42:20.92" personId="{50860DAD-A217-40AC-975A-03A6080E2F06}" id="{7D5D9D06-3A77-4519-9FE9-7C2A54490A0A}">
+    <text>Fuente: INE Chile, Serie histórica empalmada IPC base 2023=100 (archivo: serie-histórica-empalmada-ipc-diciembre-2009-a-la-fecha-xls.xlsx)</text>
+  </threadedComment>
+  <threadedComment ref="C23" dT="2026-07-02T15:34:13.48" personId="{50860DAD-A217-40AC-975A-03A6080E2F06}" id="{0A050290-AA01-430C-ADCE-D319815F4916}">
+    <text>Fuente: UF_IVP_UTM_F.xlsx, hoja Cuadro (UF fin de mes)</text>
+  </threadedComment>
+  <threadedComment ref="C28" dT="2026-07-02T15:42:20.92" personId="{50860DAD-A217-40AC-975A-03A6080E2F06}" id="{88033D7C-3197-4733-8F1C-B124922716CB}">
+    <text>Fuente: INE Chile, Serie histórica empalmada IPC base 2023=100 (archivo: serie-histórica-empalmada-ipc-diciembre-2009-a-la-fecha-xls.xlsx)</text>
+  </threadedComment>
+  <threadedComment ref="C31" dT="2026-07-02T15:34:13.48" personId="{50860DAD-A217-40AC-975A-03A6080E2F06}" id="{A0044274-CA02-4FE0-8A5C-DF1392887D40}">
+    <text>Fuente: UF_IVP_UTM_F.xlsx, hoja Cuadro (UF fin de mes)</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -794,10 +1001,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BV7"/>
+  <dimension ref="A1:BV31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.109375" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" customWidth="1"/>
     <col min="4" max="4" width="11.5546875" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" customWidth="1"/>
@@ -2187,6 +2395,2763 @@
         <v>42626</v>
       </c>
     </row>
+    <row r="9" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="T9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="U9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="V9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="W9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y9" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AQ9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AS9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AV9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AW9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AY9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="AZ9" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="BA9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="BB9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="BC9" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="BD9" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="BE9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="BF9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="BG9" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="BH9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="BI9" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="BJ9" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="BK9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="BL9" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="BM9" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="BN9" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="BO9" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="BP9" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="BQ9" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="BR9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="BS9" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="BT9" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="BU9" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="BV9" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="2"/>
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="2"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="2"/>
+      <c r="AI10" s="2"/>
+      <c r="AJ10" s="2"/>
+      <c r="AK10" s="2"/>
+      <c r="AL10" s="2"/>
+      <c r="AM10" s="2"/>
+      <c r="AN10" s="4"/>
+      <c r="AO10" s="2"/>
+      <c r="AP10" s="2"/>
+      <c r="AQ10" s="2"/>
+      <c r="AR10" s="2"/>
+      <c r="AS10" s="2"/>
+      <c r="AT10" s="2"/>
+      <c r="AU10" s="2"/>
+      <c r="AV10" s="2"/>
+      <c r="AW10" s="2"/>
+      <c r="AX10" s="2"/>
+      <c r="AY10" s="2"/>
+      <c r="AZ10" s="2"/>
+      <c r="BA10" s="2"/>
+      <c r="BB10" s="2"/>
+      <c r="BC10" s="2"/>
+      <c r="BD10" s="2"/>
+      <c r="BE10" s="2"/>
+      <c r="BF10" s="2"/>
+      <c r="BG10" s="2"/>
+      <c r="BH10" s="2"/>
+      <c r="BI10" s="2"/>
+      <c r="BJ10" s="2"/>
+      <c r="BK10" s="2"/>
+    </row>
+    <row r="11" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="5">
+        <v>820.10666670000001</v>
+      </c>
+      <c r="D11" s="5">
+        <v>806.77449999999999</v>
+      </c>
+      <c r="E11" s="5">
+        <v>798.75130430000002</v>
+      </c>
+      <c r="F11" s="5">
+        <v>818.26300000000003</v>
+      </c>
+      <c r="G11" s="5">
+        <v>848.18863639999995</v>
+      </c>
+      <c r="H11" s="5">
+        <v>863.15599999999995</v>
+      </c>
+      <c r="I11" s="5">
+        <v>952.42142850000005</v>
+      </c>
+      <c r="J11" s="5">
+        <v>904.03136370000004</v>
+      </c>
+      <c r="K11" s="5">
+        <v>924.11749999999995</v>
+      </c>
+      <c r="L11" s="5">
+        <v>954.63736840000001</v>
+      </c>
+      <c r="M11" s="5">
+        <v>915.07523809999998</v>
+      </c>
+      <c r="N11" s="5">
+        <v>873.80619049999996</v>
+      </c>
+      <c r="O11" s="5">
+        <v>823.87952380000002</v>
+      </c>
+      <c r="P11" s="5">
+        <v>799.54200000000003</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>807.78391309999995</v>
+      </c>
+      <c r="R11" s="5">
+        <v>804.51526309999997</v>
+      </c>
+      <c r="S11" s="5">
+        <v>799.01318179999998</v>
+      </c>
+      <c r="T11" s="5">
+        <v>799.375</v>
+      </c>
+      <c r="U11" s="5">
+        <v>815.25571430000002</v>
+      </c>
+      <c r="V11" s="5">
+        <v>856.25818179999999</v>
+      </c>
+      <c r="W11" s="5">
+        <v>886.60052629999996</v>
+      </c>
+      <c r="X11" s="5">
+        <v>926.53899999999999</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>885.19142859999999</v>
+      </c>
+      <c r="Z11" s="5">
+        <v>875.06368420000001</v>
+      </c>
+      <c r="AA11" s="5">
+        <v>910.4931818</v>
+      </c>
+      <c r="AB11" s="5">
+        <v>965.23523809999995</v>
+      </c>
+      <c r="AC11" s="5">
+        <v>968.52250000000004</v>
+      </c>
+      <c r="AD11" s="5">
+        <v>958.89</v>
+      </c>
+      <c r="AE11" s="5">
+        <v>916.09238100000005</v>
+      </c>
+      <c r="AF11" s="5">
+        <v>927.53210520000005</v>
+      </c>
+      <c r="AG11" s="5">
+        <v>937.53545459999998</v>
+      </c>
+      <c r="AH11" s="5">
+        <v>928.47666660000004</v>
+      </c>
+      <c r="AI11" s="5">
+        <v>925.30833340000004</v>
+      </c>
+      <c r="AJ11" s="5">
+        <v>936.70363629999997</v>
+      </c>
+      <c r="AK11" s="5">
+        <v>972.41849999999999</v>
+      </c>
+      <c r="AL11" s="5">
+        <v>983.23599999999999</v>
+      </c>
+      <c r="AM11" s="5">
+        <v>1000.2072727</v>
+      </c>
+      <c r="AN11" s="5">
+        <v>955.12</v>
+      </c>
+      <c r="AO11" s="5">
+        <v>932.49714289999997</v>
+      </c>
+      <c r="AP11" s="5">
+        <v>962.0809524</v>
+      </c>
+      <c r="AQ11" s="5">
+        <v>940.32749999999999</v>
+      </c>
+      <c r="AR11" s="5">
+        <v>937.60950000000003</v>
+      </c>
+      <c r="AS11" s="5">
+        <v>953.52181810000002</v>
+      </c>
+      <c r="AT11" s="5">
+        <v>965.72749999999996</v>
+      </c>
+      <c r="AU11" s="5">
+        <v>960.22299999999996</v>
+      </c>
+      <c r="AV11" s="5">
+        <v>953.12318189999996</v>
+      </c>
+      <c r="AW11" s="5">
+        <v>934.92100000000005</v>
+      </c>
+      <c r="AX11" s="6">
+        <v>915.11149999999998</v>
+      </c>
+      <c r="AY11" s="5">
+        <v>881.9642857</v>
+      </c>
+      <c r="AZ11" s="5">
+        <v>862.33550000000002</v>
+      </c>
+      <c r="BA11" s="5">
+        <v>912.4409091</v>
+      </c>
+      <c r="BB11" s="5">
+        <v>896.72380950000002</v>
+      </c>
+      <c r="BC11" s="5">
+        <v>896.98473690000003</v>
+      </c>
+      <c r="BD11" s="5">
+        <v>900</v>
+      </c>
+      <c r="BE11" s="5">
+        <v>900</v>
+      </c>
+      <c r="BF11" s="5">
+        <v>900</v>
+      </c>
+      <c r="BG11" s="5">
+        <v>900</v>
+      </c>
+      <c r="BH11" s="5">
+        <v>900</v>
+      </c>
+      <c r="BI11" s="5">
+        <v>900</v>
+      </c>
+      <c r="BJ11" s="5">
+        <v>900</v>
+      </c>
+      <c r="BK11" s="5">
+        <v>910</v>
+      </c>
+      <c r="BL11" s="5">
+        <v>910</v>
+      </c>
+      <c r="BM11" s="5">
+        <v>910</v>
+      </c>
+      <c r="BN11" s="5">
+        <v>910</v>
+      </c>
+      <c r="BO11" s="5">
+        <v>910</v>
+      </c>
+      <c r="BP11" s="5">
+        <v>910</v>
+      </c>
+      <c r="BQ11" s="5">
+        <v>910</v>
+      </c>
+      <c r="BR11" s="5">
+        <v>910</v>
+      </c>
+      <c r="BS11" s="5">
+        <v>910</v>
+      </c>
+      <c r="BT11" s="5">
+        <v>910</v>
+      </c>
+      <c r="BU11" s="5">
+        <v>910</v>
+      </c>
+      <c r="BV11" s="5">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="12" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="10">
+        <v>87.23</v>
+      </c>
+      <c r="D12" s="10">
+        <v>87.48</v>
+      </c>
+      <c r="E12" s="10">
+        <v>89.11</v>
+      </c>
+      <c r="F12" s="10">
+        <v>90.35</v>
+      </c>
+      <c r="G12" s="10">
+        <v>91.43</v>
+      </c>
+      <c r="H12" s="10">
+        <v>92.29</v>
+      </c>
+      <c r="I12" s="10">
+        <v>93.56</v>
+      </c>
+      <c r="J12" s="10">
+        <v>94.69</v>
+      </c>
+      <c r="K12" s="10">
+        <v>95.51</v>
+      </c>
+      <c r="L12" s="10">
+        <v>96</v>
+      </c>
+      <c r="M12" s="10">
+        <v>96.94</v>
+      </c>
+      <c r="N12" s="10">
+        <v>97.21</v>
+      </c>
+      <c r="O12" s="10">
+        <v>98</v>
+      </c>
+      <c r="P12" s="10">
+        <v>97.93</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>99</v>
+      </c>
+      <c r="R12" s="10">
+        <v>99.3</v>
+      </c>
+      <c r="S12" s="10">
+        <v>99.41</v>
+      </c>
+      <c r="T12" s="10">
+        <v>99.26</v>
+      </c>
+      <c r="U12" s="10">
+        <v>99.61</v>
+      </c>
+      <c r="V12" s="10">
+        <v>99.72</v>
+      </c>
+      <c r="W12" s="10">
+        <v>100.39</v>
+      </c>
+      <c r="X12" s="10">
+        <v>100.84</v>
+      </c>
+      <c r="Y12" s="10">
+        <v>101.59</v>
+      </c>
+      <c r="Z12" s="10">
+        <v>101.04</v>
+      </c>
+      <c r="AA12" s="10">
+        <v>101.72</v>
+      </c>
+      <c r="AB12" s="10">
+        <v>102.32</v>
+      </c>
+      <c r="AC12" s="10">
+        <v>102.7</v>
+      </c>
+      <c r="AD12" s="10">
+        <v>103.24</v>
+      </c>
+      <c r="AE12" s="10">
+        <v>103.52</v>
+      </c>
+      <c r="AF12" s="10">
+        <v>103.42</v>
+      </c>
+      <c r="AG12" s="10">
+        <v>104.19</v>
+      </c>
+      <c r="AH12" s="10">
+        <v>104.45</v>
+      </c>
+      <c r="AI12" s="10">
+        <v>104.54</v>
+      </c>
+      <c r="AJ12" s="10">
+        <v>105.56</v>
+      </c>
+      <c r="AK12" s="10">
+        <v>105.83</v>
+      </c>
+      <c r="AL12" s="10">
+        <v>105.62</v>
+      </c>
+      <c r="AM12" s="10">
+        <v>106.74</v>
+      </c>
+      <c r="AN12" s="10">
+        <v>107.16</v>
+      </c>
+      <c r="AO12" s="10">
+        <v>107.7</v>
+      </c>
+      <c r="AP12" s="10">
+        <v>107.91</v>
+      </c>
+      <c r="AQ12" s="10">
+        <v>108.12</v>
+      </c>
+      <c r="AR12" s="10">
+        <v>107.68</v>
+      </c>
+      <c r="AS12" s="10">
+        <v>108.62</v>
+      </c>
+      <c r="AT12" s="10">
+        <v>108.66</v>
+      </c>
+      <c r="AU12" s="10">
+        <v>109.14</v>
+      </c>
+      <c r="AV12" s="10">
+        <v>109.19</v>
+      </c>
+      <c r="AW12" s="10">
+        <v>109.47</v>
+      </c>
+      <c r="AX12" s="10">
+        <v>109.26</v>
+      </c>
+      <c r="AY12" s="10">
+        <v>109.71</v>
+      </c>
+      <c r="AZ12" s="10">
+        <v>109.7</v>
+      </c>
+      <c r="BA12" s="10">
+        <v>110.75</v>
+      </c>
+      <c r="BB12" s="10">
+        <v>112.18</v>
+      </c>
+      <c r="BC12" s="10">
+        <v>112.37</v>
+      </c>
+      <c r="BD12" s="5">
+        <v>112.8</v>
+      </c>
+      <c r="BE12" s="5">
+        <v>113.19</v>
+      </c>
+      <c r="BF12" s="5">
+        <v>113.59</v>
+      </c>
+      <c r="BG12" s="5">
+        <v>113.99</v>
+      </c>
+      <c r="BH12" s="5">
+        <v>114.39</v>
+      </c>
+      <c r="BI12" s="5">
+        <v>114.79</v>
+      </c>
+      <c r="BJ12" s="5">
+        <v>113.96</v>
+      </c>
+      <c r="BK12" s="5">
+        <v>114.25</v>
+      </c>
+      <c r="BL12" s="5">
+        <v>114.54</v>
+      </c>
+      <c r="BM12" s="5">
+        <v>114.83</v>
+      </c>
+      <c r="BN12" s="5">
+        <v>115.12</v>
+      </c>
+      <c r="BO12" s="5">
+        <v>115.42</v>
+      </c>
+      <c r="BP12" s="5">
+        <v>115.71</v>
+      </c>
+      <c r="BQ12" s="5">
+        <v>116.01</v>
+      </c>
+      <c r="BR12" s="5">
+        <v>116.3</v>
+      </c>
+      <c r="BS12" s="5">
+        <v>116.6</v>
+      </c>
+      <c r="BT12" s="5">
+        <v>116.89</v>
+      </c>
+      <c r="BU12" s="5">
+        <v>117.19</v>
+      </c>
+      <c r="BV12" s="5">
+        <v>117.49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="5">
+        <v>115.77</v>
+      </c>
+      <c r="D13" s="5">
+        <v>116.1</v>
+      </c>
+      <c r="E13" s="5">
+        <v>118.26</v>
+      </c>
+      <c r="F13" s="5">
+        <v>119.91</v>
+      </c>
+      <c r="G13" s="5">
+        <v>121.35</v>
+      </c>
+      <c r="H13" s="5">
+        <v>122.48</v>
+      </c>
+      <c r="I13" s="5">
+        <v>124.16</v>
+      </c>
+      <c r="J13" s="5">
+        <v>125.67</v>
+      </c>
+      <c r="K13" s="5">
+        <v>126.75</v>
+      </c>
+      <c r="L13" s="5">
+        <v>127.38374999999999</v>
+      </c>
+      <c r="M13" s="5">
+        <v>128.65</v>
+      </c>
+      <c r="N13" s="5">
+        <v>129.02000000000001</v>
+      </c>
+      <c r="O13" s="5">
+        <v>130.05000000000001</v>
+      </c>
+      <c r="P13" s="5">
+        <v>129.97</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>131.38</v>
+      </c>
+      <c r="R13" s="5">
+        <v>131.79</v>
+      </c>
+      <c r="S13" s="5">
+        <v>131.94</v>
+      </c>
+      <c r="T13" s="5">
+        <v>131.74</v>
+      </c>
+      <c r="U13" s="5">
+        <v>132.19999999999999</v>
+      </c>
+      <c r="V13" s="5">
+        <v>132.35</v>
+      </c>
+      <c r="W13" s="5">
+        <v>133.24</v>
+      </c>
+      <c r="X13" s="5">
+        <v>133.82</v>
+      </c>
+      <c r="Y13" s="5">
+        <v>134.82</v>
+      </c>
+      <c r="Z13" s="5">
+        <v>134.1</v>
+      </c>
+      <c r="AA13" s="5">
+        <v>101.72</v>
+      </c>
+      <c r="AB13" s="5">
+        <v>102.32</v>
+      </c>
+      <c r="AC13" s="5">
+        <v>102.7</v>
+      </c>
+      <c r="AD13" s="5">
+        <v>103.24</v>
+      </c>
+      <c r="AE13" s="5">
+        <v>103.52</v>
+      </c>
+      <c r="AF13" s="5">
+        <v>103.42</v>
+      </c>
+      <c r="AG13" s="5">
+        <v>104.19</v>
+      </c>
+      <c r="AH13" s="5">
+        <v>104.45</v>
+      </c>
+      <c r="AI13" s="5">
+        <v>104.54</v>
+      </c>
+      <c r="AJ13" s="5">
+        <v>105.56</v>
+      </c>
+      <c r="AK13" s="5">
+        <v>105.83</v>
+      </c>
+      <c r="AL13" s="5">
+        <v>105.62</v>
+      </c>
+      <c r="AM13" s="5">
+        <v>106.74</v>
+      </c>
+      <c r="AN13" s="7">
+        <v>107.16</v>
+      </c>
+      <c r="AO13" s="7">
+        <v>107.7</v>
+      </c>
+      <c r="AP13" s="7">
+        <v>107.91</v>
+      </c>
+      <c r="AQ13" s="7">
+        <v>108.12</v>
+      </c>
+      <c r="AR13" s="7">
+        <v>107.68</v>
+      </c>
+      <c r="AS13" s="7">
+        <v>108.62</v>
+      </c>
+      <c r="AT13" s="7">
+        <v>108.66</v>
+      </c>
+      <c r="AU13" s="7">
+        <v>109.14</v>
+      </c>
+      <c r="AV13" s="7">
+        <v>109.19</v>
+      </c>
+      <c r="AW13" s="7">
+        <v>109.47</v>
+      </c>
+      <c r="AX13" s="7">
+        <v>109.26</v>
+      </c>
+      <c r="AY13" s="5">
+        <v>109.71</v>
+      </c>
+      <c r="AZ13" s="5">
+        <v>109.7</v>
+      </c>
+      <c r="BA13" s="5">
+        <v>110.75</v>
+      </c>
+      <c r="BB13" s="5">
+        <v>112.18</v>
+      </c>
+      <c r="BC13" s="5">
+        <v>112.37</v>
+      </c>
+      <c r="BD13" s="5">
+        <v>112.8</v>
+      </c>
+      <c r="BE13" s="5">
+        <v>113.19</v>
+      </c>
+      <c r="BF13" s="5">
+        <v>113.59</v>
+      </c>
+      <c r="BG13" s="5">
+        <v>113.99</v>
+      </c>
+      <c r="BH13" s="5">
+        <v>114.39</v>
+      </c>
+      <c r="BI13" s="5">
+        <v>114.79</v>
+      </c>
+      <c r="BJ13" s="5">
+        <v>113.96</v>
+      </c>
+      <c r="BK13" s="5"/>
+      <c r="BL13" s="5"/>
+      <c r="BM13" s="5"/>
+      <c r="BN13" s="5"/>
+      <c r="BO13" s="5"/>
+      <c r="BP13" s="5"/>
+      <c r="BQ13" s="5"/>
+      <c r="BR13" s="5"/>
+      <c r="BS13" s="5"/>
+      <c r="BT13" s="5"/>
+      <c r="BU13" s="5"/>
+      <c r="BV13" s="5"/>
+    </row>
+    <row r="14" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="7">
+        <v>281.14800000000002</v>
+      </c>
+      <c r="D14" s="7">
+        <v>283.71600000000001</v>
+      </c>
+      <c r="E14" s="7">
+        <v>287.50400000000002</v>
+      </c>
+      <c r="F14" s="7">
+        <v>289.10899999999998</v>
+      </c>
+      <c r="G14" s="7">
+        <v>292.29599999999999</v>
+      </c>
+      <c r="H14" s="7">
+        <v>296.31099999999998</v>
+      </c>
+      <c r="I14" s="7">
+        <v>296.27600000000001</v>
+      </c>
+      <c r="J14" s="7">
+        <v>296.17099999999999</v>
+      </c>
+      <c r="K14" s="7">
+        <v>296.80799999999999</v>
+      </c>
+      <c r="L14" s="7">
+        <v>298.012</v>
+      </c>
+      <c r="M14" s="7">
+        <v>297.71100000000001</v>
+      </c>
+      <c r="N14" s="7">
+        <v>296.79700000000003</v>
+      </c>
+      <c r="O14" s="7">
+        <v>299.17</v>
+      </c>
+      <c r="P14" s="7">
+        <v>300.83999999999997</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>301.83600000000001</v>
+      </c>
+      <c r="R14" s="7">
+        <v>303.363</v>
+      </c>
+      <c r="S14" s="7">
+        <v>304.12700000000001</v>
+      </c>
+      <c r="T14" s="7">
+        <v>305.10899999999998</v>
+      </c>
+      <c r="U14" s="7">
+        <v>305.69099999999997</v>
+      </c>
+      <c r="V14" s="7">
+        <v>307.02600000000001</v>
+      </c>
+      <c r="W14" s="7">
+        <v>307.78899999999999</v>
+      </c>
+      <c r="X14" s="7">
+        <v>307.67099999999999</v>
+      </c>
+      <c r="Y14" s="7">
+        <v>307.05099999999999</v>
+      </c>
+      <c r="Z14" s="7">
+        <v>306.99599999999998</v>
+      </c>
+      <c r="AA14" s="7">
+        <v>308.41699999999997</v>
+      </c>
+      <c r="AB14" s="7">
+        <v>310.32600000000002</v>
+      </c>
+      <c r="AC14" s="7">
+        <v>312.33199999999999</v>
+      </c>
+      <c r="AD14" s="7">
+        <v>313.548</v>
+      </c>
+      <c r="AE14" s="7">
+        <v>314.06900000000002</v>
+      </c>
+      <c r="AF14" s="7">
+        <v>314.17500000000001</v>
+      </c>
+      <c r="AG14" s="7">
+        <v>314.54000000000002</v>
+      </c>
+      <c r="AH14" s="7">
+        <v>314.79599999999999</v>
+      </c>
+      <c r="AI14" s="7">
+        <v>315.30099999999999</v>
+      </c>
+      <c r="AJ14" s="7">
+        <v>315.66399999999999</v>
+      </c>
+      <c r="AK14" s="7">
+        <v>315.49299999999999</v>
+      </c>
+      <c r="AL14" s="7">
+        <v>315.58764789999998</v>
+      </c>
+      <c r="AM14" s="7">
+        <v>317.67099999999999</v>
+      </c>
+      <c r="AN14" s="7">
+        <v>319.08199999999999</v>
+      </c>
+      <c r="AO14" s="7">
+        <v>319.79899999999998</v>
+      </c>
+      <c r="AP14" s="7">
+        <v>320.79500000000002</v>
+      </c>
+      <c r="AQ14" s="7">
+        <v>321.46499999999997</v>
+      </c>
+      <c r="AR14" s="7">
+        <v>322.56099999999998</v>
+      </c>
+      <c r="AS14" s="7">
+        <v>323.048</v>
+      </c>
+      <c r="AT14" s="7">
+        <v>323.976</v>
+      </c>
+      <c r="AU14" s="7">
+        <v>324.8</v>
+      </c>
+      <c r="AV14" s="11">
+        <v>324.46100000000001</v>
+      </c>
+      <c r="AW14" s="7">
+        <v>324.12200000000001</v>
+      </c>
+      <c r="AX14" s="7">
+        <v>324.05399999999997</v>
+      </c>
+      <c r="AY14" s="7">
+        <v>325.25200000000001</v>
+      </c>
+      <c r="AZ14" s="7">
+        <v>326.78500000000003</v>
+      </c>
+      <c r="BA14" s="7">
+        <v>330.21300000000002</v>
+      </c>
+      <c r="BB14" s="7">
+        <v>333.02</v>
+      </c>
+      <c r="BC14" s="7">
+        <v>335.12299999999999</v>
+      </c>
+      <c r="BD14" s="5">
+        <v>335.31</v>
+      </c>
+      <c r="BE14" s="5">
+        <v>336.46</v>
+      </c>
+      <c r="BF14" s="5">
+        <v>337.62</v>
+      </c>
+      <c r="BG14" s="5">
+        <v>338.78</v>
+      </c>
+      <c r="BH14" s="5">
+        <v>339.95</v>
+      </c>
+      <c r="BI14" s="5">
+        <v>341.11</v>
+      </c>
+      <c r="BJ14" s="5">
+        <v>337.67</v>
+      </c>
+      <c r="BK14" s="5">
+        <v>338.41</v>
+      </c>
+      <c r="BL14" s="5">
+        <v>339.17</v>
+      </c>
+      <c r="BM14" s="5">
+        <v>339.92</v>
+      </c>
+      <c r="BN14" s="5">
+        <v>340.68</v>
+      </c>
+      <c r="BO14" s="5">
+        <v>341.43</v>
+      </c>
+      <c r="BP14" s="5">
+        <v>342.19</v>
+      </c>
+      <c r="BQ14" s="5">
+        <v>342.95</v>
+      </c>
+      <c r="BR14" s="5">
+        <v>343.71</v>
+      </c>
+      <c r="BS14" s="5">
+        <v>344.48</v>
+      </c>
+      <c r="BT14" s="5">
+        <v>345.24</v>
+      </c>
+      <c r="BU14" s="5">
+        <v>346.01</v>
+      </c>
+      <c r="BV14" s="5">
+        <v>346.78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="7">
+        <v>31212.65</v>
+      </c>
+      <c r="D15" s="7">
+        <v>31539.200000000001</v>
+      </c>
+      <c r="E15" s="7">
+        <v>31727.74</v>
+      </c>
+      <c r="F15" s="7">
+        <v>32176.49</v>
+      </c>
+      <c r="G15" s="7">
+        <v>32679.54</v>
+      </c>
+      <c r="H15" s="7">
+        <v>33086.83</v>
+      </c>
+      <c r="I15" s="7">
+        <v>33417.26</v>
+      </c>
+      <c r="J15" s="7">
+        <v>33836.51</v>
+      </c>
+      <c r="K15" s="7">
+        <v>34258.230000000003</v>
+      </c>
+      <c r="L15" s="7">
+        <v>34600.35</v>
+      </c>
+      <c r="M15" s="7">
+        <v>34811.800000000003</v>
+      </c>
+      <c r="N15" s="7">
+        <v>35110.980000000003</v>
+      </c>
+      <c r="O15" s="7">
+        <v>35287.5</v>
+      </c>
+      <c r="P15" s="7">
+        <v>35509.68</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>35575.480000000003</v>
+      </c>
+      <c r="R15" s="7">
+        <v>35838.550000000003</v>
+      </c>
+      <c r="S15" s="7">
+        <v>36032.89</v>
+      </c>
+      <c r="T15" s="7">
+        <v>36089.480000000003</v>
+      </c>
+      <c r="U15" s="7">
+        <v>36049.050000000003</v>
+      </c>
+      <c r="V15" s="7">
+        <v>36130.31</v>
+      </c>
+      <c r="W15" s="7">
+        <v>36197.53</v>
+      </c>
+      <c r="X15" s="7">
+        <v>36388.07</v>
+      </c>
+      <c r="Y15" s="7">
+        <v>36563.870000000003</v>
+      </c>
+      <c r="Z15" s="7">
+        <v>36789.360000000001</v>
+      </c>
+      <c r="AA15" s="7">
+        <v>36733.040000000001</v>
+      </c>
+      <c r="AB15" s="7">
+        <v>36856.5</v>
+      </c>
+      <c r="AC15" s="7">
+        <v>37093.519999999997</v>
+      </c>
+      <c r="AD15" s="7">
+        <v>37261.980000000003</v>
+      </c>
+      <c r="AE15" s="7">
+        <v>37438.910000000003</v>
+      </c>
+      <c r="AF15" s="7">
+        <v>37571.86</v>
+      </c>
+      <c r="AG15" s="7">
+        <v>37578.949999999997</v>
+      </c>
+      <c r="AH15" s="7">
+        <v>37754.47</v>
+      </c>
+      <c r="AI15" s="7">
+        <v>37910.42</v>
+      </c>
+      <c r="AJ15" s="7">
+        <v>37971.42</v>
+      </c>
+      <c r="AK15" s="7">
+        <v>38247.919999999998</v>
+      </c>
+      <c r="AL15" s="7">
+        <v>38416.69</v>
+      </c>
+      <c r="AM15" s="7">
+        <v>38384.410000000003</v>
+      </c>
+      <c r="AN15" s="7">
+        <v>38647.94</v>
+      </c>
+      <c r="AO15" s="7">
+        <v>38894.11</v>
+      </c>
+      <c r="AP15" s="7">
+        <v>39075.410000000003</v>
+      </c>
+      <c r="AQ15" s="7">
+        <v>39189.449999999997</v>
+      </c>
+      <c r="AR15" s="7">
+        <v>39267.07</v>
+      </c>
+      <c r="AS15" s="7">
+        <v>39179.01</v>
+      </c>
+      <c r="AT15" s="7">
+        <v>39383.07</v>
+      </c>
+      <c r="AU15" s="7">
+        <v>39485.65</v>
+      </c>
+      <c r="AV15" s="7">
+        <v>39597.67</v>
+      </c>
+      <c r="AW15" s="7">
+        <v>39643.589999999997</v>
+      </c>
+      <c r="AX15" s="7">
+        <v>39727.96</v>
+      </c>
+      <c r="AY15" s="7">
+        <v>39706.07</v>
+      </c>
+      <c r="AZ15" s="7">
+        <v>39790.629999999997</v>
+      </c>
+      <c r="BA15" s="7">
+        <v>39841.72</v>
+      </c>
+      <c r="BB15" s="7">
+        <v>40120.199999999997</v>
+      </c>
+      <c r="BC15" s="7">
+        <v>40610.69</v>
+      </c>
+      <c r="BD15" s="5">
+        <v>40820.31</v>
+      </c>
+      <c r="BE15" s="5">
+        <v>40896.699999999997</v>
+      </c>
+      <c r="BF15" s="5">
+        <v>41040.400000000001</v>
+      </c>
+      <c r="BG15" s="5">
+        <v>41184.6</v>
+      </c>
+      <c r="BH15" s="5">
+        <v>41329.4</v>
+      </c>
+      <c r="BI15" s="5">
+        <v>41474.6</v>
+      </c>
+      <c r="BJ15" s="5">
+        <v>41173.699999999997</v>
+      </c>
+      <c r="BK15" s="5">
+        <v>41449</v>
+      </c>
+      <c r="BL15" s="5">
+        <v>41555</v>
+      </c>
+      <c r="BM15" s="5">
+        <v>41661</v>
+      </c>
+      <c r="BN15" s="5">
+        <v>41767</v>
+      </c>
+      <c r="BO15" s="5">
+        <v>41873</v>
+      </c>
+      <c r="BP15" s="5">
+        <v>41980</v>
+      </c>
+      <c r="BQ15" s="5">
+        <v>42087</v>
+      </c>
+      <c r="BR15" s="5">
+        <v>42194</v>
+      </c>
+      <c r="BS15" s="5">
+        <v>42302</v>
+      </c>
+      <c r="BT15" s="5">
+        <v>42409</v>
+      </c>
+      <c r="BU15" s="5">
+        <v>42517</v>
+      </c>
+      <c r="BV15" s="5">
+        <v>42626</v>
+      </c>
+    </row>
+    <row r="17" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="8"/>
+      <c r="AA17" s="8"/>
+      <c r="AB17" s="8"/>
+      <c r="AC17" s="8"/>
+      <c r="AD17" s="8"/>
+      <c r="AE17" s="8"/>
+      <c r="AF17" s="8"/>
+      <c r="AG17" s="8"/>
+      <c r="AH17" s="8"/>
+      <c r="AI17" s="8"/>
+      <c r="AJ17" s="8"/>
+      <c r="AK17" s="8"/>
+      <c r="AL17" s="8"/>
+      <c r="AM17" s="3"/>
+      <c r="AN17" s="3"/>
+      <c r="AO17" s="3"/>
+      <c r="AP17" s="3"/>
+      <c r="AQ17" s="3"/>
+      <c r="AR17" s="3"/>
+      <c r="AS17" s="3"/>
+      <c r="AT17" s="3"/>
+      <c r="AU17" s="3"/>
+      <c r="AV17" s="3"/>
+      <c r="AW17" s="3"/>
+      <c r="AX17" s="3"/>
+      <c r="AY17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="AZ17" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="BA17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="BB17" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="BC17" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="BD17" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="BE17" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="BF17" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="BG17" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="BH17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="BI17" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="BJ17" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="BK17" s="8"/>
+      <c r="BL17" s="8"/>
+      <c r="BM17" s="8"/>
+      <c r="BN17" s="8"/>
+      <c r="BO17" s="8"/>
+      <c r="BP17" s="8"/>
+      <c r="BQ17" s="8"/>
+      <c r="BR17" s="8"/>
+      <c r="BS17" s="8"/>
+      <c r="BT17" s="8"/>
+      <c r="BU17" s="8"/>
+      <c r="BV17" s="8"/>
+    </row>
+    <row r="18" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+      <c r="AA18" s="2"/>
+      <c r="AB18" s="2"/>
+      <c r="AC18" s="2"/>
+      <c r="AD18" s="2"/>
+      <c r="AE18" s="2"/>
+      <c r="AF18" s="2"/>
+      <c r="AG18" s="2"/>
+      <c r="AH18" s="2"/>
+      <c r="AI18" s="2"/>
+      <c r="AJ18" s="2"/>
+      <c r="AK18" s="2"/>
+      <c r="AL18" s="2"/>
+      <c r="AM18" s="2"/>
+      <c r="AN18" s="4"/>
+      <c r="AO18" s="2"/>
+      <c r="AP18" s="2"/>
+      <c r="AQ18" s="2"/>
+      <c r="AR18" s="2"/>
+      <c r="AS18" s="2"/>
+      <c r="AT18" s="2"/>
+      <c r="AU18" s="2"/>
+      <c r="AV18" s="2"/>
+      <c r="AW18" s="2"/>
+      <c r="AX18" s="2"/>
+      <c r="AY18" s="2"/>
+      <c r="AZ18" s="2"/>
+      <c r="BA18" s="2"/>
+      <c r="BB18" s="2"/>
+      <c r="BC18" s="2"/>
+      <c r="BD18" s="2"/>
+      <c r="BE18" s="2"/>
+      <c r="BF18" s="2"/>
+      <c r="BG18" s="2"/>
+      <c r="BH18" s="2"/>
+      <c r="BI18" s="2"/>
+      <c r="BJ18" s="2"/>
+      <c r="BK18" s="2"/>
+    </row>
+    <row r="19" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="5"/>
+      <c r="AA19" s="5"/>
+      <c r="AB19" s="5"/>
+      <c r="AC19" s="5"/>
+      <c r="AD19" s="5"/>
+      <c r="AE19" s="5"/>
+      <c r="AF19" s="5"/>
+      <c r="AG19" s="5"/>
+      <c r="AH19" s="5"/>
+      <c r="AI19" s="5"/>
+      <c r="AJ19" s="5"/>
+      <c r="AK19" s="5"/>
+      <c r="AL19" s="5"/>
+      <c r="AM19" s="5"/>
+      <c r="AN19" s="5"/>
+      <c r="AO19" s="5"/>
+      <c r="AP19" s="5"/>
+      <c r="AQ19" s="5"/>
+      <c r="AR19" s="5"/>
+      <c r="AS19" s="5"/>
+      <c r="AT19" s="5"/>
+      <c r="AU19" s="5"/>
+      <c r="AV19" s="5"/>
+      <c r="AW19" s="5"/>
+      <c r="AX19" s="6"/>
+      <c r="AY19" s="5">
+        <v>881.9642857</v>
+      </c>
+      <c r="AZ19" s="5">
+        <v>862.33550000000002</v>
+      </c>
+      <c r="BA19" s="5">
+        <v>912.4409091</v>
+      </c>
+      <c r="BB19" s="5">
+        <v>896.72380950000002</v>
+      </c>
+      <c r="BC19" s="5">
+        <v>896.98473690000003</v>
+      </c>
+      <c r="BD19" s="12">
+        <v>900</v>
+      </c>
+      <c r="BE19" s="12">
+        <v>900</v>
+      </c>
+      <c r="BF19" s="12">
+        <v>900</v>
+      </c>
+      <c r="BG19" s="12">
+        <v>900</v>
+      </c>
+      <c r="BH19" s="12">
+        <v>900</v>
+      </c>
+      <c r="BI19" s="12">
+        <v>900</v>
+      </c>
+      <c r="BJ19" s="12">
+        <v>900</v>
+      </c>
+      <c r="BK19" s="5"/>
+      <c r="BL19" s="5"/>
+      <c r="BM19" s="5"/>
+      <c r="BN19" s="5"/>
+      <c r="BO19" s="5"/>
+      <c r="BP19" s="5"/>
+      <c r="BQ19" s="5"/>
+      <c r="BR19" s="5"/>
+      <c r="BS19" s="5"/>
+      <c r="BT19" s="5"/>
+      <c r="BU19" s="5"/>
+      <c r="BV19" s="5"/>
+    </row>
+    <row r="20" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="10"/>
+      <c r="AA20" s="10"/>
+      <c r="AB20" s="10"/>
+      <c r="AC20" s="10"/>
+      <c r="AD20" s="10"/>
+      <c r="AE20" s="10"/>
+      <c r="AF20" s="10"/>
+      <c r="AG20" s="10"/>
+      <c r="AH20" s="10"/>
+      <c r="AI20" s="10"/>
+      <c r="AJ20" s="10"/>
+      <c r="AK20" s="10"/>
+      <c r="AL20" s="10"/>
+      <c r="AM20" s="10"/>
+      <c r="AN20" s="10"/>
+      <c r="AO20" s="10"/>
+      <c r="AP20" s="10"/>
+      <c r="AQ20" s="10"/>
+      <c r="AR20" s="10"/>
+      <c r="AS20" s="10"/>
+      <c r="AT20" s="10"/>
+      <c r="AU20" s="10"/>
+      <c r="AV20" s="10"/>
+      <c r="AW20" s="10"/>
+      <c r="AX20" s="10"/>
+      <c r="AY20" s="10">
+        <v>109.71</v>
+      </c>
+      <c r="AZ20" s="10">
+        <v>109.7</v>
+      </c>
+      <c r="BA20" s="10">
+        <v>110.75</v>
+      </c>
+      <c r="BB20" s="10">
+        <v>112.18</v>
+      </c>
+      <c r="BC20" s="10">
+        <v>112.37</v>
+      </c>
+      <c r="BD20" s="12">
+        <v>112.8</v>
+      </c>
+      <c r="BE20" s="12">
+        <v>113.19</v>
+      </c>
+      <c r="BF20" s="12">
+        <v>113.59</v>
+      </c>
+      <c r="BG20" s="12">
+        <v>113.99</v>
+      </c>
+      <c r="BH20" s="12">
+        <v>114.39</v>
+      </c>
+      <c r="BI20" s="12">
+        <v>114.79</v>
+      </c>
+      <c r="BJ20" s="12">
+        <v>113.96</v>
+      </c>
+      <c r="BK20" s="5"/>
+      <c r="BL20" s="5"/>
+      <c r="BM20" s="5"/>
+      <c r="BN20" s="5"/>
+      <c r="BO20" s="5"/>
+      <c r="BP20" s="5"/>
+      <c r="BQ20" s="5"/>
+      <c r="BR20" s="5"/>
+      <c r="BS20" s="5"/>
+      <c r="BT20" s="5"/>
+      <c r="BU20" s="5"/>
+      <c r="BV20" s="5"/>
+    </row>
+    <row r="21" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="5"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="5"/>
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="5"/>
+      <c r="AG21" s="5"/>
+      <c r="AH21" s="5"/>
+      <c r="AI21" s="5"/>
+      <c r="AJ21" s="5"/>
+      <c r="AK21" s="5"/>
+      <c r="AL21" s="5"/>
+      <c r="AM21" s="5"/>
+      <c r="AN21" s="7"/>
+      <c r="AO21" s="7"/>
+      <c r="AP21" s="7"/>
+      <c r="AQ21" s="7"/>
+      <c r="AR21" s="7"/>
+      <c r="AS21" s="7"/>
+      <c r="AT21" s="7"/>
+      <c r="AU21" s="7"/>
+      <c r="AV21" s="7"/>
+      <c r="AW21" s="7"/>
+      <c r="AX21" s="7"/>
+      <c r="AY21" s="5">
+        <v>109.71</v>
+      </c>
+      <c r="AZ21" s="5">
+        <v>109.7</v>
+      </c>
+      <c r="BA21" s="5">
+        <v>110.75</v>
+      </c>
+      <c r="BB21" s="5">
+        <v>112.18</v>
+      </c>
+      <c r="BC21" s="5">
+        <v>112.37</v>
+      </c>
+      <c r="BD21" s="12">
+        <v>112.8</v>
+      </c>
+      <c r="BE21" s="12">
+        <v>113.19</v>
+      </c>
+      <c r="BF21" s="12">
+        <v>113.59</v>
+      </c>
+      <c r="BG21" s="12">
+        <v>113.99</v>
+      </c>
+      <c r="BH21" s="12">
+        <v>114.39</v>
+      </c>
+      <c r="BI21" s="12">
+        <v>114.79</v>
+      </c>
+      <c r="BJ21" s="12">
+        <v>113.96</v>
+      </c>
+      <c r="BK21" s="5"/>
+      <c r="BL21" s="5"/>
+      <c r="BM21" s="5"/>
+      <c r="BN21" s="5"/>
+      <c r="BO21" s="5"/>
+      <c r="BP21" s="5"/>
+      <c r="BQ21" s="5"/>
+      <c r="BR21" s="5"/>
+      <c r="BS21" s="5"/>
+      <c r="BT21" s="5"/>
+      <c r="BU21" s="5"/>
+      <c r="BV21" s="5"/>
+    </row>
+    <row r="22" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="7"/>
+      <c r="Z22" s="7"/>
+      <c r="AA22" s="7"/>
+      <c r="AB22" s="7"/>
+      <c r="AC22" s="7"/>
+      <c r="AD22" s="7"/>
+      <c r="AE22" s="7"/>
+      <c r="AF22" s="7"/>
+      <c r="AG22" s="7"/>
+      <c r="AH22" s="7"/>
+      <c r="AI22" s="7"/>
+      <c r="AJ22" s="7"/>
+      <c r="AK22" s="7"/>
+      <c r="AL22" s="7"/>
+      <c r="AM22" s="7"/>
+      <c r="AN22" s="7"/>
+      <c r="AO22" s="7"/>
+      <c r="AP22" s="7"/>
+      <c r="AQ22" s="7"/>
+      <c r="AR22" s="7"/>
+      <c r="AS22" s="7"/>
+      <c r="AT22" s="7"/>
+      <c r="AU22" s="7"/>
+      <c r="AV22" s="11"/>
+      <c r="AW22" s="7"/>
+      <c r="AX22" s="7"/>
+      <c r="AY22" s="7">
+        <v>325.25200000000001</v>
+      </c>
+      <c r="AZ22" s="7">
+        <v>326.78500000000003</v>
+      </c>
+      <c r="BA22" s="7">
+        <v>330.21300000000002</v>
+      </c>
+      <c r="BB22" s="7">
+        <v>333.02</v>
+      </c>
+      <c r="BC22" s="7">
+        <v>335.12299999999999</v>
+      </c>
+      <c r="BD22" s="12">
+        <v>335.31</v>
+      </c>
+      <c r="BE22" s="12">
+        <v>336.46</v>
+      </c>
+      <c r="BF22" s="12">
+        <v>337.62</v>
+      </c>
+      <c r="BG22" s="12">
+        <v>338.78</v>
+      </c>
+      <c r="BH22" s="12">
+        <v>339.95</v>
+      </c>
+      <c r="BI22" s="12">
+        <v>341.11</v>
+      </c>
+      <c r="BJ22" s="12">
+        <v>337.67</v>
+      </c>
+      <c r="BK22" s="5"/>
+      <c r="BL22" s="5"/>
+      <c r="BM22" s="5"/>
+      <c r="BN22" s="5"/>
+      <c r="BO22" s="5"/>
+      <c r="BP22" s="5"/>
+      <c r="BQ22" s="5"/>
+      <c r="BR22" s="5"/>
+      <c r="BS22" s="5"/>
+      <c r="BT22" s="5"/>
+      <c r="BU22" s="5"/>
+      <c r="BV22" s="5"/>
+    </row>
+    <row r="23" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+      <c r="Z23" s="7"/>
+      <c r="AA23" s="7"/>
+      <c r="AB23" s="7"/>
+      <c r="AC23" s="7"/>
+      <c r="AD23" s="7"/>
+      <c r="AE23" s="7"/>
+      <c r="AF23" s="7"/>
+      <c r="AG23" s="7"/>
+      <c r="AH23" s="7"/>
+      <c r="AI23" s="7"/>
+      <c r="AJ23" s="7"/>
+      <c r="AK23" s="7"/>
+      <c r="AL23" s="7"/>
+      <c r="AM23" s="7"/>
+      <c r="AN23" s="7"/>
+      <c r="AO23" s="7"/>
+      <c r="AP23" s="7"/>
+      <c r="AQ23" s="7"/>
+      <c r="AR23" s="7"/>
+      <c r="AS23" s="7"/>
+      <c r="AT23" s="7"/>
+      <c r="AU23" s="7"/>
+      <c r="AV23" s="7"/>
+      <c r="AW23" s="7"/>
+      <c r="AX23" s="7"/>
+      <c r="AY23" s="7">
+        <v>39706.07</v>
+      </c>
+      <c r="AZ23" s="7">
+        <v>39790.629999999997</v>
+      </c>
+      <c r="BA23" s="7">
+        <v>39841.72</v>
+      </c>
+      <c r="BB23" s="7">
+        <v>40120.199999999997</v>
+      </c>
+      <c r="BC23" s="7">
+        <v>40610.69</v>
+      </c>
+      <c r="BD23" s="12">
+        <v>40820.31</v>
+      </c>
+      <c r="BE23" s="12">
+        <v>40896.699999999997</v>
+      </c>
+      <c r="BF23" s="12">
+        <v>41040.400000000001</v>
+      </c>
+      <c r="BG23" s="12">
+        <v>41184.6</v>
+      </c>
+      <c r="BH23" s="12">
+        <v>41329.4</v>
+      </c>
+      <c r="BI23" s="12">
+        <v>41474.6</v>
+      </c>
+      <c r="BJ23" s="12">
+        <v>41173.699999999997</v>
+      </c>
+      <c r="BK23" s="5"/>
+      <c r="BL23" s="5"/>
+      <c r="BM23" s="5"/>
+      <c r="BN23" s="5"/>
+      <c r="BO23" s="5"/>
+      <c r="BP23" s="5"/>
+      <c r="BQ23" s="5"/>
+      <c r="BR23" s="5"/>
+      <c r="BS23" s="5"/>
+      <c r="BT23" s="5"/>
+      <c r="BU23" s="5"/>
+      <c r="BV23" s="5"/>
+    </row>
+    <row r="25" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="8"/>
+      <c r="X25" s="8"/>
+      <c r="Y25" s="8"/>
+      <c r="Z25" s="8"/>
+      <c r="AA25" s="8"/>
+      <c r="AB25" s="8"/>
+      <c r="AC25" s="8"/>
+      <c r="AD25" s="8"/>
+      <c r="AE25" s="8"/>
+      <c r="AF25" s="8"/>
+      <c r="AG25" s="8"/>
+      <c r="AH25" s="8"/>
+      <c r="AI25" s="8"/>
+      <c r="AJ25" s="8"/>
+      <c r="AK25" s="8"/>
+      <c r="AL25" s="8"/>
+      <c r="AM25" s="3"/>
+      <c r="AN25" s="3"/>
+      <c r="AO25" s="3"/>
+      <c r="AP25" s="3"/>
+      <c r="AQ25" s="3"/>
+      <c r="AR25" s="3"/>
+      <c r="AS25" s="3"/>
+      <c r="AT25" s="3"/>
+      <c r="AU25" s="3"/>
+      <c r="AV25" s="3"/>
+      <c r="AW25" s="3"/>
+      <c r="AX25" s="3"/>
+      <c r="AY25" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="AZ25" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="BA25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="BB25" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="BC25" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="BD25" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="BE25" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="BF25" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="BG25" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="BH25" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="BI25" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="BJ25" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="BK25" s="8"/>
+      <c r="BL25" s="8"/>
+      <c r="BM25" s="8"/>
+      <c r="BN25" s="8"/>
+      <c r="BO25" s="8"/>
+      <c r="BP25" s="8"/>
+      <c r="BQ25" s="8"/>
+      <c r="BR25" s="8"/>
+      <c r="BS25" s="8"/>
+      <c r="BT25" s="8"/>
+      <c r="BU25" s="8"/>
+      <c r="BV25" s="8"/>
+    </row>
+    <row r="26" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
+      <c r="Z26" s="2"/>
+      <c r="AA26" s="2"/>
+      <c r="AB26" s="2"/>
+      <c r="AC26" s="2"/>
+      <c r="AD26" s="2"/>
+      <c r="AE26" s="2"/>
+      <c r="AF26" s="2"/>
+      <c r="AG26" s="2"/>
+      <c r="AH26" s="2"/>
+      <c r="AI26" s="2"/>
+      <c r="AJ26" s="2"/>
+      <c r="AK26" s="2"/>
+      <c r="AL26" s="2"/>
+      <c r="AM26" s="2"/>
+      <c r="AN26" s="4"/>
+      <c r="AO26" s="2"/>
+      <c r="AP26" s="2"/>
+      <c r="AQ26" s="2"/>
+      <c r="AR26" s="2"/>
+      <c r="AS26" s="2"/>
+      <c r="AT26" s="2"/>
+      <c r="AU26" s="2"/>
+      <c r="AV26" s="2"/>
+      <c r="AW26" s="2"/>
+      <c r="AX26" s="2"/>
+      <c r="AY26" s="2"/>
+      <c r="AZ26" s="2"/>
+      <c r="BA26" s="2"/>
+      <c r="BB26" s="2"/>
+      <c r="BC26" s="2"/>
+      <c r="BD26" s="2"/>
+      <c r="BE26" s="2"/>
+      <c r="BF26" s="2"/>
+      <c r="BG26" s="2"/>
+      <c r="BH26" s="2"/>
+      <c r="BI26" s="2"/>
+      <c r="BJ26" s="2"/>
+      <c r="BK26" s="2"/>
+    </row>
+    <row r="27" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="5"/>
+      <c r="Y27" s="5"/>
+      <c r="Z27" s="5"/>
+      <c r="AA27" s="5"/>
+      <c r="AB27" s="5"/>
+      <c r="AC27" s="5"/>
+      <c r="AD27" s="5"/>
+      <c r="AE27" s="5"/>
+      <c r="AF27" s="5"/>
+      <c r="AG27" s="5"/>
+      <c r="AH27" s="5"/>
+      <c r="AI27" s="5"/>
+      <c r="AJ27" s="5"/>
+      <c r="AK27" s="5"/>
+      <c r="AL27" s="5"/>
+      <c r="AM27" s="5"/>
+      <c r="AN27" s="5"/>
+      <c r="AO27" s="5"/>
+      <c r="AP27" s="5"/>
+      <c r="AQ27" s="5"/>
+      <c r="AR27" s="5"/>
+      <c r="AS27" s="5"/>
+      <c r="AT27" s="5"/>
+      <c r="AU27" s="5"/>
+      <c r="AV27" s="5"/>
+      <c r="AW27" s="5"/>
+      <c r="AX27" s="6"/>
+      <c r="AY27" s="5">
+        <v>881.9642857</v>
+      </c>
+      <c r="AZ27" s="5">
+        <v>862.33550000000002</v>
+      </c>
+      <c r="BA27" s="5">
+        <v>912.4409091</v>
+      </c>
+      <c r="BB27" s="5">
+        <v>896.72380950000002</v>
+      </c>
+      <c r="BC27" s="5">
+        <v>896.98473690000003</v>
+      </c>
+      <c r="BD27" s="5">
+        <v>900</v>
+      </c>
+      <c r="BE27" s="12">
+        <v>900</v>
+      </c>
+      <c r="BF27" s="12">
+        <v>900</v>
+      </c>
+      <c r="BG27" s="12">
+        <v>900</v>
+      </c>
+      <c r="BH27" s="12">
+        <v>900</v>
+      </c>
+      <c r="BI27" s="12">
+        <v>900</v>
+      </c>
+      <c r="BJ27" s="12">
+        <v>900</v>
+      </c>
+      <c r="BK27" s="5"/>
+      <c r="BL27" s="5"/>
+      <c r="BM27" s="5"/>
+      <c r="BN27" s="5"/>
+      <c r="BO27" s="5"/>
+      <c r="BP27" s="5"/>
+      <c r="BQ27" s="5"/>
+      <c r="BR27" s="5"/>
+      <c r="BS27" s="5"/>
+      <c r="BT27" s="5"/>
+      <c r="BU27" s="5"/>
+      <c r="BV27" s="5"/>
+    </row>
+    <row r="28" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
+      <c r="T28" s="10"/>
+      <c r="U28" s="10"/>
+      <c r="V28" s="10"/>
+      <c r="W28" s="10"/>
+      <c r="X28" s="10"/>
+      <c r="Y28" s="10"/>
+      <c r="Z28" s="10"/>
+      <c r="AA28" s="10"/>
+      <c r="AB28" s="10"/>
+      <c r="AC28" s="10"/>
+      <c r="AD28" s="10"/>
+      <c r="AE28" s="10"/>
+      <c r="AF28" s="10"/>
+      <c r="AG28" s="10"/>
+      <c r="AH28" s="10"/>
+      <c r="AI28" s="10"/>
+      <c r="AJ28" s="10"/>
+      <c r="AK28" s="10"/>
+      <c r="AL28" s="10"/>
+      <c r="AM28" s="10"/>
+      <c r="AN28" s="10"/>
+      <c r="AO28" s="10"/>
+      <c r="AP28" s="10"/>
+      <c r="AQ28" s="10"/>
+      <c r="AR28" s="10"/>
+      <c r="AS28" s="10"/>
+      <c r="AT28" s="10"/>
+      <c r="AU28" s="10"/>
+      <c r="AV28" s="10"/>
+      <c r="AW28" s="10"/>
+      <c r="AX28" s="10"/>
+      <c r="AY28" s="10">
+        <v>109.71</v>
+      </c>
+      <c r="AZ28" s="10">
+        <v>109.7</v>
+      </c>
+      <c r="BA28" s="10">
+        <v>110.75</v>
+      </c>
+      <c r="BB28" s="10">
+        <v>112.18</v>
+      </c>
+      <c r="BC28" s="10">
+        <v>112.37</v>
+      </c>
+      <c r="BD28" s="5">
+        <v>112.8</v>
+      </c>
+      <c r="BE28" s="12">
+        <v>113.19</v>
+      </c>
+      <c r="BF28" s="12">
+        <v>113.59</v>
+      </c>
+      <c r="BG28" s="12">
+        <v>113.99</v>
+      </c>
+      <c r="BH28" s="12">
+        <v>114.39</v>
+      </c>
+      <c r="BI28" s="12">
+        <v>114.79</v>
+      </c>
+      <c r="BJ28" s="12">
+        <v>113.96</v>
+      </c>
+      <c r="BK28" s="5"/>
+      <c r="BL28" s="5"/>
+      <c r="BM28" s="5"/>
+      <c r="BN28" s="5"/>
+      <c r="BO28" s="5"/>
+      <c r="BP28" s="5"/>
+      <c r="BQ28" s="5"/>
+      <c r="BR28" s="5"/>
+      <c r="BS28" s="5"/>
+      <c r="BT28" s="5"/>
+      <c r="BU28" s="5"/>
+      <c r="BV28" s="5"/>
+    </row>
+    <row r="29" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5"/>
+      <c r="Z29" s="5"/>
+      <c r="AA29" s="5"/>
+      <c r="AB29" s="5"/>
+      <c r="AC29" s="5"/>
+      <c r="AD29" s="5"/>
+      <c r="AE29" s="5"/>
+      <c r="AF29" s="5"/>
+      <c r="AG29" s="5"/>
+      <c r="AH29" s="5"/>
+      <c r="AI29" s="5"/>
+      <c r="AJ29" s="5"/>
+      <c r="AK29" s="5"/>
+      <c r="AL29" s="5"/>
+      <c r="AM29" s="5"/>
+      <c r="AN29" s="7"/>
+      <c r="AO29" s="7"/>
+      <c r="AP29" s="7"/>
+      <c r="AQ29" s="7"/>
+      <c r="AR29" s="7"/>
+      <c r="AS29" s="7"/>
+      <c r="AT29" s="7"/>
+      <c r="AU29" s="7"/>
+      <c r="AV29" s="7"/>
+      <c r="AW29" s="7"/>
+      <c r="AX29" s="7"/>
+      <c r="AY29" s="5">
+        <v>109.71</v>
+      </c>
+      <c r="AZ29" s="5">
+        <v>109.7</v>
+      </c>
+      <c r="BA29" s="5">
+        <v>110.75</v>
+      </c>
+      <c r="BB29" s="5">
+        <v>112.18</v>
+      </c>
+      <c r="BC29" s="5">
+        <v>112.37</v>
+      </c>
+      <c r="BD29" s="5">
+        <v>112.8</v>
+      </c>
+      <c r="BE29" s="12">
+        <v>113.19</v>
+      </c>
+      <c r="BF29" s="12">
+        <v>113.59</v>
+      </c>
+      <c r="BG29" s="12">
+        <v>113.99</v>
+      </c>
+      <c r="BH29" s="12">
+        <v>114.39</v>
+      </c>
+      <c r="BI29" s="12">
+        <v>114.79</v>
+      </c>
+      <c r="BJ29" s="12">
+        <v>113.96</v>
+      </c>
+      <c r="BK29" s="5"/>
+      <c r="BL29" s="5"/>
+      <c r="BM29" s="5"/>
+      <c r="BN29" s="5"/>
+      <c r="BO29" s="5"/>
+      <c r="BP29" s="5"/>
+      <c r="BQ29" s="5"/>
+      <c r="BR29" s="5"/>
+      <c r="BS29" s="5"/>
+      <c r="BT29" s="5"/>
+      <c r="BU29" s="5"/>
+      <c r="BV29" s="5"/>
+    </row>
+    <row r="30" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="7"/>
+      <c r="W30" s="7"/>
+      <c r="X30" s="7"/>
+      <c r="Y30" s="7"/>
+      <c r="Z30" s="7"/>
+      <c r="AA30" s="7"/>
+      <c r="AB30" s="7"/>
+      <c r="AC30" s="7"/>
+      <c r="AD30" s="7"/>
+      <c r="AE30" s="7"/>
+      <c r="AF30" s="7"/>
+      <c r="AG30" s="7"/>
+      <c r="AH30" s="7"/>
+      <c r="AI30" s="7"/>
+      <c r="AJ30" s="7"/>
+      <c r="AK30" s="7"/>
+      <c r="AL30" s="7"/>
+      <c r="AM30" s="7"/>
+      <c r="AN30" s="7"/>
+      <c r="AO30" s="7"/>
+      <c r="AP30" s="7"/>
+      <c r="AQ30" s="7"/>
+      <c r="AR30" s="7"/>
+      <c r="AS30" s="7"/>
+      <c r="AT30" s="7"/>
+      <c r="AU30" s="7"/>
+      <c r="AV30" s="11"/>
+      <c r="AW30" s="7"/>
+      <c r="AX30" s="7"/>
+      <c r="AY30" s="7">
+        <v>325.25200000000001</v>
+      </c>
+      <c r="AZ30" s="7">
+        <v>326.78500000000003</v>
+      </c>
+      <c r="BA30" s="7">
+        <v>330.21300000000002</v>
+      </c>
+      <c r="BB30" s="7">
+        <v>333.02</v>
+      </c>
+      <c r="BC30" s="7">
+        <v>335.12299999999999</v>
+      </c>
+      <c r="BD30" s="5">
+        <v>335.31</v>
+      </c>
+      <c r="BE30" s="12">
+        <v>336.46</v>
+      </c>
+      <c r="BF30" s="12">
+        <v>337.62</v>
+      </c>
+      <c r="BG30" s="12">
+        <v>338.78</v>
+      </c>
+      <c r="BH30" s="12">
+        <v>339.95</v>
+      </c>
+      <c r="BI30" s="12">
+        <v>341.11</v>
+      </c>
+      <c r="BJ30" s="12">
+        <v>337.67</v>
+      </c>
+      <c r="BK30" s="5"/>
+      <c r="BL30" s="5"/>
+      <c r="BM30" s="5"/>
+      <c r="BN30" s="5"/>
+      <c r="BO30" s="5"/>
+      <c r="BP30" s="5"/>
+      <c r="BQ30" s="5"/>
+      <c r="BR30" s="5"/>
+      <c r="BS30" s="5"/>
+      <c r="BT30" s="5"/>
+      <c r="BU30" s="5"/>
+      <c r="BV30" s="5"/>
+    </row>
+    <row r="31" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
+      <c r="Y31" s="7"/>
+      <c r="Z31" s="7"/>
+      <c r="AA31" s="7"/>
+      <c r="AB31" s="7"/>
+      <c r="AC31" s="7"/>
+      <c r="AD31" s="7"/>
+      <c r="AE31" s="7"/>
+      <c r="AF31" s="7"/>
+      <c r="AG31" s="7"/>
+      <c r="AH31" s="7"/>
+      <c r="AI31" s="7"/>
+      <c r="AJ31" s="7"/>
+      <c r="AK31" s="7"/>
+      <c r="AL31" s="7"/>
+      <c r="AM31" s="7"/>
+      <c r="AN31" s="7"/>
+      <c r="AO31" s="7"/>
+      <c r="AP31" s="7"/>
+      <c r="AQ31" s="7"/>
+      <c r="AR31" s="7"/>
+      <c r="AS31" s="7"/>
+      <c r="AT31" s="7"/>
+      <c r="AU31" s="7"/>
+      <c r="AV31" s="7"/>
+      <c r="AW31" s="7"/>
+      <c r="AX31" s="7"/>
+      <c r="AY31" s="7">
+        <v>39706.07</v>
+      </c>
+      <c r="AZ31" s="7">
+        <v>39790.629999999997</v>
+      </c>
+      <c r="BA31" s="7">
+        <v>39841.72</v>
+      </c>
+      <c r="BB31" s="7">
+        <v>40120.199999999997</v>
+      </c>
+      <c r="BC31" s="7">
+        <v>40610.69</v>
+      </c>
+      <c r="BD31" s="5">
+        <v>40820.31</v>
+      </c>
+      <c r="BE31" s="12">
+        <v>40896.699999999997</v>
+      </c>
+      <c r="BF31" s="12">
+        <v>41040.400000000001</v>
+      </c>
+      <c r="BG31" s="12">
+        <v>41184.6</v>
+      </c>
+      <c r="BH31" s="12">
+        <v>41329.4</v>
+      </c>
+      <c r="BI31" s="12">
+        <v>41474.6</v>
+      </c>
+      <c r="BJ31" s="12">
+        <v>41173.699999999997</v>
+      </c>
+      <c r="BK31" s="5"/>
+      <c r="BL31" s="5"/>
+      <c r="BM31" s="5"/>
+      <c r="BN31" s="5"/>
+      <c r="BO31" s="5"/>
+      <c r="BP31" s="5"/>
+      <c r="BQ31" s="5"/>
+      <c r="BR31" s="5"/>
+      <c r="BS31" s="5"/>
+      <c r="BT31" s="5"/>
+      <c r="BU31" s="5"/>
+      <c r="BV31" s="5"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
